--- a/artfynd/A 11882-2026 artfynd.xlsx
+++ b/artfynd/A 11882-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949769</v>
       </c>
       <c r="B2" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11882-2026 artfynd.xlsx
+++ b/artfynd/A 11882-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949769</v>
       </c>
       <c r="B2" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11882-2026 artfynd.xlsx
+++ b/artfynd/A 11882-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949769</v>
       </c>
       <c r="B2" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11882-2026 artfynd.xlsx
+++ b/artfynd/A 11882-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949769</v>
       </c>
       <c r="B2" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11882-2026 artfynd.xlsx
+++ b/artfynd/A 11882-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949769</v>
       </c>
       <c r="B2" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11882-2026 artfynd.xlsx
+++ b/artfynd/A 11882-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949769</v>
       </c>
       <c r="B2" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11882-2026 artfynd.xlsx
+++ b/artfynd/A 11882-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949769</v>
       </c>
       <c r="B2" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11882-2026 artfynd.xlsx
+++ b/artfynd/A 11882-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949769</v>
       </c>
       <c r="B2" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11882-2026 artfynd.xlsx
+++ b/artfynd/A 11882-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949769</v>
       </c>
       <c r="B2" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11882-2026 artfynd.xlsx
+++ b/artfynd/A 11882-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949769</v>
       </c>
       <c r="B2" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11882-2026 artfynd.xlsx
+++ b/artfynd/A 11882-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949769</v>
       </c>
       <c r="B2" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11882-2026 artfynd.xlsx
+++ b/artfynd/A 11882-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949769</v>
       </c>
       <c r="B2" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11882-2026 artfynd.xlsx
+++ b/artfynd/A 11882-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949769</v>
       </c>
       <c r="B2" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11882-2026 artfynd.xlsx
+++ b/artfynd/A 11882-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949769</v>
       </c>
       <c r="B2" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11882-2026 artfynd.xlsx
+++ b/artfynd/A 11882-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949769</v>
       </c>
       <c r="B2" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11882-2026 artfynd.xlsx
+++ b/artfynd/A 11882-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949769</v>
       </c>
       <c r="B2" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11882-2026 artfynd.xlsx
+++ b/artfynd/A 11882-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949769</v>
       </c>
       <c r="B2" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11882-2026 artfynd.xlsx
+++ b/artfynd/A 11882-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949769</v>
       </c>
       <c r="B2" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11882-2026 artfynd.xlsx
+++ b/artfynd/A 11882-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949769</v>
       </c>
       <c r="B2" t="n">
-        <v>101650</v>
+        <v>101651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11882-2026 artfynd.xlsx
+++ b/artfynd/A 11882-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949769</v>
       </c>
       <c r="B2" t="n">
-        <v>101651</v>
+        <v>101654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
